--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1662,6 +1662,254 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114925931</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57385</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579515</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6584849</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ekoskådning</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114927308</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57252</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579510</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6584852</v>
+      </c>
+      <c r="S11" t="n">
+        <v>35</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Björn Skogsberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Björn Skogsberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,6 +1910,610 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114925947</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579515</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6584849</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ekoskådning</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114928404</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579522</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6584853</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Mellquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Mellquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114927315</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579510</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6584852</v>
+      </c>
+      <c r="S14" t="n">
+        <v>35</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Björn Skogsberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Björn Skogsberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114928413</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579522</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6584853</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Mellquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Mellquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114927321</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579510</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6584852</v>
+      </c>
+      <c r="S16" t="n">
+        <v>35</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Björn Skogsberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Björn Skogsberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -2267,7 +2267,7 @@
         <v>120976411</v>
       </c>
       <c r="B15" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>121246118</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>121271549</v>
       </c>
       <c r="B17" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -2391,7 +2391,7 @@
         <v>121246118</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>121271549</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113092264</v>
+        <v>103871392</v>
       </c>
       <c r="B6" t="n">
-        <v>56785</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,25 +1180,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1210,23 +1210,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579510</v>
+        <v>579535</v>
       </c>
       <c r="R6" t="n">
-        <v>6584852</v>
+        <v>6584868</v>
       </c>
       <c r="S6" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,22 +1250,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,22 +1280,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ekoskådning</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113092267</v>
+        <v>105020342</v>
       </c>
       <c r="B7" t="n">
-        <v>56911</v>
+        <v>57508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,23 +1338,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579510</v>
+        <v>579535</v>
       </c>
       <c r="R7" t="n">
-        <v>6584852</v>
+        <v>6584868</v>
       </c>
       <c r="S7" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1378,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2022-12-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2022-12-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,22 +1408,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113484602</v>
+        <v>113092264</v>
       </c>
       <c r="B8" t="n">
-        <v>57624</v>
+        <v>56785</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,21 +1436,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1498,22 +1502,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-12-02</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-12-02</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113589668</v>
+        <v>113092267</v>
       </c>
       <c r="B9" t="n">
-        <v>57624</v>
+        <v>56911</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,49 +1556,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+          <t>Hällby Skogskyrkogård, matningen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579522</v>
+        <v>579510</v>
       </c>
       <c r="R9" t="n">
-        <v>6584853</v>
+        <v>6584852</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1618,22 +1626,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,22 +1656,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Björn Skogsberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Björn Skogsberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113589540</v>
+        <v>113484602</v>
       </c>
       <c r="B10" t="n">
-        <v>57414</v>
+        <v>57624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,25 +1680,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1708,17 +1716,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+          <t>Hällby Skogskyrkogård, matningen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579522</v>
+        <v>579510</v>
       </c>
       <c r="R10" t="n">
-        <v>6584853</v>
+        <v>6584852</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1742,22 +1750,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-12-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-12-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,22 +1780,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Björn Skogsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Björn Skogsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114072577</v>
+        <v>113589668</v>
       </c>
       <c r="B11" t="n">
-        <v>57414</v>
+        <v>57624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,53 +1804,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hällby fågelmatning, Srm</t>
+          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579515</v>
+        <v>579522</v>
       </c>
       <c r="R11" t="n">
-        <v>6584823</v>
+        <v>6584853</v>
       </c>
       <c r="S11" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1866,22 +1870,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1896,22 +1900,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114928413</v>
+        <v>113589540</v>
       </c>
       <c r="B12" t="n">
-        <v>57916</v>
+        <v>57414</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,33 +1924,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1986,22 +1994,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,10 +2036,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114927308</v>
+        <v>114072577</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
+        <v>57414</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,45 +2052,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+          <t>Hällby fågelmatning, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579510</v>
+        <v>579515</v>
       </c>
       <c r="R13" t="n">
-        <v>6584852</v>
+        <v>6584823</v>
       </c>
       <c r="S13" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2106,22 +2118,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,19 +2148,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114927321</v>
+        <v>114928413</v>
       </c>
       <c r="B14" t="n">
         <v>57916</v>
@@ -2184,21 +2196,25 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579510</v>
+        <v>579522</v>
       </c>
       <c r="R14" t="n">
-        <v>6584852</v>
+        <v>6584853</v>
       </c>
       <c r="S14" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2227,7 +2243,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2237,7 +2253,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2252,22 +2268,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120976411</v>
+        <v>114927308</v>
       </c>
       <c r="B15" t="n">
-        <v>57504</v>
+        <v>57281</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2280,49 +2296,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Matning Hällbyskogen, Srm</t>
+          <t>Hällby Skogskyrkogård, matningen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579532</v>
+        <v>579510</v>
       </c>
       <c r="R15" t="n">
-        <v>6584849</v>
+        <v>6584852</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2346,22 +2358,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2376,22 +2388,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lasse Eisele</t>
+          <t>Björn Skogsberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lasse Eisele</t>
+          <t>Björn Skogsberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121246118</v>
+        <v>114925947</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>58032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2404,16 +2416,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2421,32 +2433,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Matning Hällbyskogen, Srm</t>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579532</v>
+        <v>579535</v>
       </c>
       <c r="R16" t="n">
-        <v>6584849</v>
+        <v>6584868</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2470,22 +2478,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,22 +2508,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lasse Eisele</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lasse Eisele</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ekoskådning</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121271549</v>
+        <v>114927321</v>
       </c>
       <c r="B17" t="n">
-        <v>57370</v>
+        <v>57916</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2524,20 +2536,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2545,24 +2557,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+          <t>Hällby Skogskyrkogård, matningen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579522</v>
+        <v>579510</v>
       </c>
       <c r="R17" t="n">
-        <v>6584853</v>
+        <v>6584852</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2586,12 +2598,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,15 +2628,493 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Björn Skogsberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Björn Skogsberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120976411</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Matning Hällbyskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>579532</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6584849</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lasse Eisele</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lasse Eisele</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121246118</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57723</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Matning Hällbyskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>579532</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6584849</v>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lasse Eisele</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lasse Eisele</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121271549</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>579522</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6584853</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Johan Mellquist</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Johan Mellquist</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>105013131</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57724</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>579535</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6584868</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-12-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-12-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -2767,7 +2767,7 @@
         <v>121246118</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57724</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>121271549</v>
       </c>
       <c r="B20" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>103871392</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>105020342</v>
       </c>
       <c r="B7" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>114925947</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58033</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>121246118</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>57725</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>121271549</v>
       </c>
       <c r="B20" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>105013131</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>57725</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>103871392</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>105020342</v>
       </c>
       <c r="B7" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>114925947</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>105013131</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>57726</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3118,10 +3118,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121764184</v>
+        <v>121764216</v>
       </c>
       <c r="B22" t="n">
-        <v>57373</v>
+        <v>58001</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121764216</v>
+        <v>121764184</v>
       </c>
       <c r="B23" t="n">
-        <v>58001</v>
+        <v>57373</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3254,20 +3254,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3118,10 +3118,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121764216</v>
+        <v>121764184</v>
       </c>
       <c r="B22" t="n">
-        <v>58001</v>
+        <v>57373</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121764184</v>
+        <v>121764216</v>
       </c>
       <c r="B23" t="n">
-        <v>57373</v>
+        <v>58001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3254,20 +3254,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3118,10 +3118,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121764184</v>
+        <v>121764216</v>
       </c>
       <c r="B22" t="n">
-        <v>57373</v>
+        <v>58009</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121764216</v>
+        <v>121764184</v>
       </c>
       <c r="B23" t="n">
-        <v>58001</v>
+        <v>57381</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3254,20 +3254,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3369,7 +3369,7 @@
         <v>121774284</v>
       </c>
       <c r="B24" t="n">
-        <v>57791</v>
+        <v>57799</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3488,6 +3488,250 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122074649</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hällby fågelmatning, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>579515</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6584823</v>
+      </c>
+      <c r="S25" t="n">
+        <v>45</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Niklas Holmström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Niklas Holmström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122074656</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57734</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hällby fågelmatning, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>579515</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6584823</v>
+      </c>
+      <c r="S26" t="n">
+        <v>45</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Niklas Holmström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Niklas Holmström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074649</v>
+        <v>122074656</v>
       </c>
       <c r="B25" t="n">
-        <v>57381</v>
+        <v>57734</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,20 +3502,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,11 +3523,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3614,10 +3610,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122074656</v>
+        <v>122074649</v>
       </c>
       <c r="B26" t="n">
-        <v>57734</v>
+        <v>57381</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3626,20 +3622,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3647,7 +3643,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3118,10 +3118,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121764216</v>
+        <v>121764184</v>
       </c>
       <c r="B22" t="n">
-        <v>58009</v>
+        <v>57385</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121764184</v>
+        <v>121764216</v>
       </c>
       <c r="B23" t="n">
-        <v>57381</v>
+        <v>58013</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3254,20 +3254,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3369,7 +3369,7 @@
         <v>121774284</v>
       </c>
       <c r="B24" t="n">
-        <v>57799</v>
+        <v>57803</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074656</v>
+        <v>122074649</v>
       </c>
       <c r="B25" t="n">
-        <v>57734</v>
+        <v>57385</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,20 +3502,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,7 +3523,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3610,10 +3614,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122074649</v>
+        <v>122074656</v>
       </c>
       <c r="B26" t="n">
-        <v>57381</v>
+        <v>57738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3622,20 +3626,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3643,11 +3647,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3118,10 +3118,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121764184</v>
+        <v>121764216</v>
       </c>
       <c r="B22" t="n">
-        <v>57385</v>
+        <v>58017</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121764216</v>
+        <v>121764184</v>
       </c>
       <c r="B23" t="n">
-        <v>58013</v>
+        <v>57388</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3254,20 +3254,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3369,7 +3369,7 @@
         <v>121774284</v>
       </c>
       <c r="B24" t="n">
-        <v>57803</v>
+        <v>57807</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074649</v>
+        <v>122074656</v>
       </c>
       <c r="B25" t="n">
-        <v>57385</v>
+        <v>57742</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,20 +3502,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,11 +3523,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3614,10 +3610,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122074656</v>
+        <v>122074649</v>
       </c>
       <c r="B26" t="n">
-        <v>57738</v>
+        <v>57388</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3626,20 +3622,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3647,7 +3643,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3118,10 +3118,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121764216</v>
+        <v>121764184</v>
       </c>
       <c r="B22" t="n">
-        <v>58017</v>
+        <v>57390</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121764184</v>
+        <v>121764216</v>
       </c>
       <c r="B23" t="n">
-        <v>57388</v>
+        <v>58019</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3254,20 +3254,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3369,7 +3369,7 @@
         <v>121774284</v>
       </c>
       <c r="B24" t="n">
-        <v>57807</v>
+        <v>57809</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074656</v>
+        <v>122074649</v>
       </c>
       <c r="B25" t="n">
-        <v>57742</v>
+        <v>57390</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,20 +3502,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,7 +3523,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3610,10 +3614,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122074649</v>
+        <v>122074656</v>
       </c>
       <c r="B26" t="n">
-        <v>57388</v>
+        <v>57744</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3622,20 +3626,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3643,11 +3647,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3118,10 +3118,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121764184</v>
+        <v>121764216</v>
       </c>
       <c r="B22" t="n">
-        <v>57390</v>
+        <v>58019</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121764216</v>
+        <v>121764184</v>
       </c>
       <c r="B23" t="n">
-        <v>58019</v>
+        <v>57390</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3254,20 +3254,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074649</v>
+        <v>122074656</v>
       </c>
       <c r="B25" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,20 +3502,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,11 +3523,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3614,10 +3610,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122074656</v>
+        <v>122074649</v>
       </c>
       <c r="B26" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3626,20 +3622,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3647,7 +3643,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074649</v>
+        <v>122074656</v>
       </c>
       <c r="B25" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,20 +3502,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,11 +3523,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3614,10 +3610,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122074656</v>
+        <v>122074649</v>
       </c>
       <c r="B26" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3626,20 +3622,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3647,7 +3643,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074656</v>
+        <v>122074649</v>
       </c>
       <c r="B25" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,20 +3502,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,7 +3523,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3610,10 +3614,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122074649</v>
+        <v>122074656</v>
       </c>
       <c r="B26" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3622,20 +3626,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3643,11 +3647,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3493,7 +3493,7 @@
         <v>122074649</v>
       </c>
       <c r="B25" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>122074656</v>
       </c>
       <c r="B26" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074649</v>
+        <v>122074656</v>
       </c>
       <c r="B25" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,20 +3502,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,11 +3523,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3614,10 +3610,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122074656</v>
+        <v>122074649</v>
       </c>
       <c r="B26" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3626,20 +3622,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3647,7 +3643,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3490,10 +3490,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074656</v>
+        <v>122074649</v>
       </c>
       <c r="B25" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,20 +3502,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3523,7 +3518,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
@@ -3610,10 +3609,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122074649</v>
+        <v>122074656</v>
       </c>
       <c r="B26" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3622,20 +3621,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3643,11 +3637,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3722,6 +3722,130 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123217368</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56821</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>579535</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6584868</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torshälla</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3727,7 +3727,7 @@
         <v>123217368</v>
       </c>
       <c r="B27" t="n">
-        <v>56821</v>
+        <v>56824</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3727,7 +3727,7 @@
         <v>123217368</v>
       </c>
       <c r="B27" t="n">
-        <v>56824</v>
+        <v>56830</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -3727,7 +3727,7 @@
         <v>123217368</v>
       </c>
       <c r="B27" t="n">
-        <v>56830</v>
+        <v>56833</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 8757-2023 artfynd.xlsx
+++ b/artfynd/A 8757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113092267</v>
+        <v>113484602</v>
       </c>
       <c r="B9" t="n">
-        <v>56911</v>
+        <v>57624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1556,25 +1556,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1626,22 +1626,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-12-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,7 +1668,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113484602</v>
+        <v>113589668</v>
       </c>
       <c r="B10" t="n">
         <v>57624</v>
@@ -1701,11 +1701,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1716,17 +1712,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579510</v>
+        <v>579522</v>
       </c>
       <c r="R10" t="n">
-        <v>6584852</v>
+        <v>6584853</v>
       </c>
       <c r="S10" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1750,22 +1746,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-12-02</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-12-02</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,22 +1776,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113589668</v>
+        <v>113589540</v>
       </c>
       <c r="B11" t="n">
-        <v>57624</v>
+        <v>57414</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1804,28 +1800,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1912,7 +1912,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113589540</v>
+        <v>114072577</v>
       </c>
       <c r="B12" t="n">
         <v>57414</v>
@@ -1947,30 +1947,30 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+          <t>Hällby fågelmatning, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579522</v>
+        <v>579515</v>
       </c>
       <c r="R12" t="n">
-        <v>6584853</v>
+        <v>6584823</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1994,22 +1994,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,22 +2024,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114072577</v>
+        <v>114928413</v>
       </c>
       <c r="B13" t="n">
-        <v>57414</v>
+        <v>57916</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2048,32 +2048,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
@@ -2084,17 +2080,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hällby fågelmatning, Srm</t>
+          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579515</v>
+        <v>579522</v>
       </c>
       <c r="R13" t="n">
-        <v>6584823</v>
+        <v>6584853</v>
       </c>
       <c r="S13" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2118,22 +2114,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,22 +2144,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114928413</v>
+        <v>114927308</v>
       </c>
       <c r="B14" t="n">
-        <v>57916</v>
+        <v>57281</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2172,20 +2168,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2193,28 +2189,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+          <t>Hällby Skogskyrkogård, matningen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579522</v>
+        <v>579510</v>
       </c>
       <c r="R14" t="n">
-        <v>6584853</v>
+        <v>6584852</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2253,7 +2249,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2268,22 +2264,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Björn Skogsberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Björn Skogsberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114927308</v>
+        <v>114925947</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
+        <v>58034</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2292,20 +2288,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2313,28 +2309,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579510</v>
+        <v>579535</v>
       </c>
       <c r="R15" t="n">
-        <v>6584852</v>
+        <v>6584868</v>
       </c>
       <c r="S15" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2363,7 +2359,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2373,7 +2369,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2388,22 +2384,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>elias ernvik</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ekoskådning</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114925947</v>
+        <v>114927321</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>57916</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2436,25 +2436,21 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Matning, Hällby skogskyrkogård, Srm</t>
+          <t>Hällby Skogskyrkogård, matningen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579535</v>
+        <v>579510</v>
       </c>
       <c r="R16" t="n">
-        <v>6584868</v>
+        <v>6584852</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2483,7 +2479,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2493,7 +2489,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,26 +2504,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>elias ernvik</t>
+          <t>Björn Skogsberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>elias ernvik</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Ekoskådning</t>
-        </is>
-      </c>
+          <t>Björn Skogsberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114927321</v>
+        <v>121246118</v>
       </c>
       <c r="B17" t="n">
-        <v>57916</v>
+        <v>57725</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2540,16 +2532,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2557,24 +2549,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hällby Skogskyrkogård, matningen, Srm</t>
+          <t>Matning Hällbyskogen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579510</v>
+        <v>579532</v>
       </c>
       <c r="R17" t="n">
-        <v>6584852</v>
+        <v>6584849</v>
       </c>
       <c r="S17" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2598,22 +2598,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,22 +2628,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>Lasse Eisele</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Skogsberg</t>
+          <t>Lasse Eisele</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120976411</v>
+        <v>121271549</v>
       </c>
       <c r="B18" t="n">
-        <v>57504</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2656,49 +2656,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Matning Hällbyskogen, Srm</t>
+          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579532</v>
+        <v>579522</v>
       </c>
       <c r="R18" t="n">
-        <v>6584849</v>
+        <v>6584853</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2722,22 +2714,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2752,22 +2734,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lasse Eisele</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lasse Eisele</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121246118</v>
+        <v>105013131</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57726</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2799,7 +2781,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2812,17 +2794,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Matning Hällbyskogen, Srm</t>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579532</v>
+        <v>579535</v>
       </c>
       <c r="R19" t="n">
-        <v>6584849</v>
+        <v>6584868</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2846,22 +2828,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2022-12-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2022-12-11</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2876,22 +2858,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lasse Eisele</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lasse Eisele</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121271549</v>
+        <v>121764216</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>58019</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2900,20 +2882,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2926,16 +2908,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579522</v>
+        <v>579535</v>
       </c>
       <c r="R20" t="n">
-        <v>6584853</v>
+        <v>6584868</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2962,12 +2952,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-12-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2982,22 +2982,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105013131</v>
+        <v>121764184</v>
       </c>
       <c r="B21" t="n">
-        <v>57726</v>
+        <v>57390</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3006,20 +3006,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3036,7 +3036,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3076,22 +3076,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-12-11</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-12-11</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3118,10 +3118,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121764216</v>
+        <v>121774284</v>
       </c>
       <c r="B22" t="n">
-        <v>58019</v>
+        <v>57809</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,25 +3130,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>102999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3160,20 +3160,20 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Matning, Hällby skogskyrkogård, Srm</t>
+          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579535</v>
+        <v>579522</v>
       </c>
       <c r="R22" t="n">
-        <v>6584868</v>
+        <v>6584853</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3200,22 +3200,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-29</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-29</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3230,22 +3230,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>elias ernvik</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>elias ernvik</t>
+          <t>Johan Mellquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121764184</v>
+        <v>122074649</v>
       </c>
       <c r="B23" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3259,11 +3259,6 @@
       </c>
       <c r="E23" t="n">
         <v>100049</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3290,17 +3285,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Matning, Hällby skogskyrkogård, Srm</t>
+          <t>Hällby fågelmatning, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579535</v>
+        <v>579515</v>
       </c>
       <c r="R23" t="n">
-        <v>6584868</v>
+        <v>6584823</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3324,22 +3319,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3354,22 +3349,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>elias ernvik</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>elias ernvik</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121774284</v>
+        <v>122074656</v>
       </c>
       <c r="B24" t="n">
-        <v>57809</v>
+        <v>57749</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3378,53 +3373,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102999</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Björktrast</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fågelmatning, Hällby skogskyrkogård, Srm</t>
+          <t>Hällby fågelmatning, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579522</v>
+        <v>579515</v>
       </c>
       <c r="R24" t="n">
-        <v>6584853</v>
+        <v>6584823</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3448,22 +3434,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3478,22 +3464,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Mellquist</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122074649</v>
+        <v>123217368</v>
       </c>
       <c r="B25" t="n">
-        <v>57395</v>
+        <v>56834</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,15 +3488,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100065</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3527,23 +3518,23 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hällby fågelmatning, Srm</t>
+          <t>Matning, Hällby skogskyrkogård, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579515</v>
+        <v>579535</v>
       </c>
       <c r="R25" t="n">
-        <v>6584823</v>
+        <v>6584868</v>
       </c>
       <c r="S25" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3567,22 +3558,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3597,254 +3588,15 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
+          <t>elias ernvik</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>122074656</v>
-      </c>
-      <c r="B26" t="n">
-        <v>57749</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>103015</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Hällby fågelmatning, Srm</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>579515</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6584823</v>
-      </c>
-      <c r="S26" t="n">
-        <v>45</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Torshälla</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Niklas Holmström</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Niklas Holmström</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>123217368</v>
-      </c>
-      <c r="B27" t="n">
-        <v>56833</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100065</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Trana</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Grus grus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Matning, Hällby skogskyrkogård, Srm</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>579535</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6584868</v>
-      </c>
-      <c r="S27" t="n">
-        <v>50</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Torshälla</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>07:44</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>07:44</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>elias ernvik</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>elias ernvik</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
